--- a/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-002_Cografya_10_Sinif_Yillik_Plani_v1.0.xlsx
+++ b/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-002_Cografya_10_Sinif_Yillik_Plani_v1.0.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.SINIF" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Açıklamalar ve Onay" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'10.SINIF'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Açıklamalar ve Onay'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="1" max="1"/>
@@ -1771,686 +1773,804 @@
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
     </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="D31:D38"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D14:D18"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="E14:E15"/>
+  </mergeCells>
+  <pageMargins left="0.39" right="0.39" top="0.55" bottom="0.55" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LGNL-CYP-CP-002 · okulapp.org&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5.3" customWidth="1" min="1" max="1"/>
+    <col width="9.01" customWidth="1" min="2" max="2"/>
+    <col width="4.77" customWidth="1" min="3" max="3"/>
+    <col width="10.6" customWidth="1" min="4" max="4"/>
+    <col width="13.78" customWidth="1" min="5" max="5"/>
+    <col width="29.68" customWidth="1" min="6" max="6"/>
+    <col width="50.88" customWidth="1" min="7" max="7"/>
+    <col width="13.25" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>[OKUL ADI]</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> 2026-2027 EĞİTİM ÖĞRETİM YILI 10. SINIF COĞRAFYA DERSİ YILLIK PLANI — AÇIKLAMALAR VE ONAY</t>
+          </r>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>ÖĞRENME KANITLARI (ÖLÇME VE DEĞERLENDİRME) — ünite/hafta bazında</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="12" t="n"/>
-      <c r="G51" s="12" t="n"/>
-      <c r="H51" s="12" t="n"/>
-    </row>
-    <row r="52" ht="45.4" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="45.4" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>1-2. haftalar</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktısı; açık uçlu sorular, performans görevi, analitik dereceli puanlama anahtarı, öz değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden merak ettikleri bir coğrafi olay, olgu veya mekâna yönelik coğrafi bakışı yansıtan kısa bir makale/rapor yazmaları istenebilir. Performans görevi; konum ve ilişki belirleme, etki sorgulama ve makale/rapor yazma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="45.4" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="45.4" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>3-5. haftalar</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; açık uçlu sorular, kontrol listesi, performans görevi, analitik dereceli puanlama anahtarı, öz değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden evlerinin yakın çevresine ait uydu görüntüsü üzerinde vektör veriler (nokta, çizgi, alan) kullanarak harita oluşturmaları istenebilir. Performans görevi; amaç belirleme, yöntem ve araç gereç kullanımı, bilgi toplama, bilgileri düzenleme, harita oluşturma ve harita kullanımı ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="45.4" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="45.4" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>6. hafta, 7. hafta, 8-9. haftalar, 10-14. haftalar</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; açık uçlu sorular, çalışma yaprağı, kontrol listesi, öz değerlendirme formu, performans görevi, analitik dereceli puanlama anahtarı kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden levha tektoniği süreci ve bu süreç sonunda oluşan yeryüzü şekilleri ile ilgili üç boyutlu model oluşturmaları ve bu modelleri sunmaları istenir. Performans görevi; hazırlık yapma, bilgi toplama, bilgileri çözümleme, model oluşturma ve sunum yapma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="45.4" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="45.4" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>15-17. haftalar, 19. hafta</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; açık uçlu sorular, çalışma yaprağı, performans görevi, analitik dereceli puanlama anahtarı, öz değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden bulundukları yerleşmenin kuruluş ve gelişiminde etkili olan doğal ve beşerî faktörlere yönelik topladığı bilgilerle ilgili sunum/kısa belgesel hazırlamaları istenebilir. Performans görevi; soru sorma, bilgi toplama, bilgileri düzenlenme, ilişki kurma, sonuç çıkarma ve sunum yapma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="45.4" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="45.4" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>20-22. haftalar, 23-24. haftalar</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; yapılandırılmış grid, çalışma yaprağı, kontrol listesi, öz değerlendirme formu, performans görevi, analitik dereceli puanlama anahtarı kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden Türkiye’de yürütülen ekonomik sektörler ve bu sektörlerin gelişimine yönelik bilgi görseli hazırlamaları istenebilir. Performans görevi; amaç belirleme, bilgi toplama, bilgileri düzenlenme, görselleştirme, sonuç çıkarma ve sunma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="56" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>25-32. haftalar</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktıları; öz/akran değerlendirme formu, tanılayıcı dallanmış ağaç, kontrol listesi, çalışma yaprağı, öğrenme günlüğü, performans görevi, analitik dereceli puanlama anahtarı kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden bir afet seçmesi, bu afetle mücadelede farklı ülkelerdeki uygulamaları incelemesi ve bu uygulamaları karşılaştırması istenebilir. Elde edilen bilgilerden yararlanarak öğrencilerin sınıfta sunum yapması sağlanabilir. Performans görevi; bilgi toplama, bilgileri düzenlenme, ilişki kurma, sonuç çıkarma ve sunum yapma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-    </row>
-    <row r="58" ht="56" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>33-34. haftalar, 35. hafta</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Öğrenme çıktısı; açık uçlu sorular, çalışma yaprağı, performans görevi, analitik dereceli puanlama anahtarı, öz değerlendirme formu kullanılarak değerlendirilebilir. Performans görevi olarak öğrencilerden Türk milletinin soyut ve somut kültürel miras ögelerinin tanınması, tanıtılması, korunması ve geliştirilmesine yönelik bir faaliyet yürütmeleri istenebilir. Bu kapsamda öğrencilerin afiş, broşür veya kamu spotu hazırlamaları sağlanabilir. Performans görevi; amaç belirleme, bilgi toplama, bilgileri düzenlenme ve görselleştirme, sonuç çıkarma ve sunma ölçütlerine göre değerlendirilebilir.</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
-    </row>
-    <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>SOSYAL - DUYGUSAL ÖĞRENME BECERİLERİ — ünite/hafta bazında</t>
         </is>
       </c>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="12" t="n"/>
-      <c r="D60" s="12" t="n"/>
-      <c r="E60" s="12" t="n"/>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="12" t="n"/>
-      <c r="H60" s="12" t="n"/>
-    </row>
-    <row r="61" ht="13.6" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+    </row>
+    <row r="13" ht="13.6" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>1-2. haftalar</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB2.1. İletişim, SDB2.2. İş Birliği</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
-    </row>
-    <row r="62" ht="45.4" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="45.4" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>3-5. haftalar, 6-7. haftalar, 8-9. haftalar, 10-14. haftalar</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>SDB1.1. Kendini Tanıma (Öz Farkındalık), SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB1.3. Kendine Uyarlama (Öz Yansıtma), SDB2.1. İletişim, SDB2.2. İş Birliği</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2" t="n"/>
-    </row>
-    <row r="63" ht="24.2" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="24.2" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>15-17. haftalar, 19. hafta</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>SDB1.1. Kendini Tanıma (Öz Farkındalık), SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB1.3. Kendine Uyarlama (Öz Yansıtma), SDB2.1. İletişim, SDB2.2. İş Birliği, SDB2.3. Sosyal Farkındalık, SDB3.3. Sorumlu Karar Verme</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-    </row>
-    <row r="64" ht="24.2" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="24.2" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>20-22. haftalar, 23-24. haftalar</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB2.1. İletişim, SDB2.3. Sosyal Farkındalık, SDB3.3. Sorumlu Karar Verme</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n"/>
-    </row>
-    <row r="65" ht="24.2" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="24.2" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>25-32. haftalar</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>SDB1.1. Kendini Tanıma (Öz Farkındalık), SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB1.3. Kendine Uyarlama (Öz Yansıtma), SDB2.1. İletişim, SDB2.3. Sosyal Farkındalık, SDB3.1. Uyum, SDB3.2. Esneklik, SDB3.3. Sorumlu Karar Verme</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="n"/>
-    </row>
-    <row r="66" ht="24.2" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="24.2" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>33-34. haftalar, 35. hafta</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>SDB1.2. Kendini Düzenleme (Öz Düzenleme), SDB2.1. İletişim, SDB2.3. Sosyal Farkındalık</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2" t="n"/>
-    </row>
-    <row r="68" ht="14" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>DEĞERLER — ünite/hafta bazında</t>
         </is>
       </c>
-      <c r="B68" s="12" t="n"/>
-      <c r="C68" s="12" t="n"/>
-      <c r="D68" s="12" t="n"/>
-      <c r="E68" s="12" t="n"/>
-      <c r="F68" s="12" t="n"/>
-      <c r="G68" s="12" t="n"/>
-      <c r="H68" s="12" t="n"/>
-    </row>
-    <row r="69" ht="13.6" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+    </row>
+    <row r="21" ht="13.6" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>1-2. haftalar</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>D9. Merhamet, D15. Sevgi, D19. Vatanseverlik</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
-    </row>
-    <row r="70" ht="13.6" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="13.6" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>3-5. haftalar</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>D3. Çalışkanlık, D8. Mahremiyet</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-    </row>
-    <row r="71" ht="34.8" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="34.8" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>6-7. haftalar, 8-9. haftalar, 10-14. haftalar</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n"/>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>D3. Çalışkanlık, D5. Duyarlılık, D14. Saygı, D16. Sorumluluk, D19. Vatanseverlik</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="n"/>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n"/>
-    </row>
-    <row r="72" ht="24.2" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="24.2" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>15-17. haftalar, 19. hafta</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n"/>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>D3. Çalışkanlık, D5. Duyarlılık, D12. Sabır</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
-    </row>
-    <row r="73" ht="24.2" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="24.2" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>20-22. haftalar, 23-24. haftalar</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>D11. Özgürlük, D3. Çalışkanlık, D19. Vatanseverlik</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="n"/>
-      <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="n"/>
-    </row>
-    <row r="74" ht="13.6" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="13.6" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>25-32. haftalar</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n"/>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>D3. Çalışkanlık, D5. Duyarlılık, D6. Dürüstlük, D12. Sabır, D16. Sorumluluk, D20. Yardımseverlik</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n"/>
-    </row>
-    <row r="75" ht="24.2" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="24.2" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>33-34. haftalar, 35. hafta</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n"/>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>D19. Vatanseverlik</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="n"/>
-      <c r="F75" s="2" t="n"/>
-      <c r="G75" s="2" t="n"/>
-      <c r="H75" s="2" t="n"/>
-    </row>
-    <row r="77" ht="14" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>OKURYAZARLIK BECERİLERİ — ünite/hafta bazında</t>
         </is>
       </c>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="12" t="n"/>
-      <c r="D77" s="12" t="n"/>
-      <c r="E77" s="12" t="n"/>
-      <c r="F77" s="12" t="n"/>
-      <c r="G77" s="12" t="n"/>
-      <c r="H77" s="12" t="n"/>
-    </row>
-    <row r="78" ht="34.8" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+    </row>
+    <row r="30" ht="34.8" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>1-2. haftalar, 15-17. haftalar, 19. hafta</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n"/>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>OB1. Bilgi Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="n"/>
-      <c r="G78" s="2" t="n"/>
-      <c r="H78" s="2" t="n"/>
-    </row>
-    <row r="79" ht="13.6" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="13.6" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>3-5. haftalar</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n"/>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>OB2. Dijital Okuryazarlık, OB4. Görsel Okuryazarlık, OB7. Veri Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="n"/>
-    </row>
-    <row r="80" ht="34.8" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="34.8" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>6-7. haftalar, 8-9. haftalar, 10-14. haftalar</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n"/>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>OB2. Dijital Okuryazarlık, OB4. Görsel Okuryazarlık</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n"/>
-      <c r="G80" s="2" t="n"/>
-      <c r="H80" s="2" t="n"/>
-    </row>
-    <row r="81" ht="24.2" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+    </row>
+    <row r="33" ht="24.2" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>20-22. haftalar, 23-24. haftalar</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n"/>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>OB3. Finansal Okuryazarlık, OB4. Görsel Okuryazarlık, OB7. Veri Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n"/>
-      <c r="E81" s="2" t="n"/>
-      <c r="F81" s="2" t="n"/>
-      <c r="G81" s="2" t="n"/>
-      <c r="H81" s="2" t="n"/>
-    </row>
-    <row r="82" ht="13.6" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="13.6" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>25-32. haftalar</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n"/>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>OB1. Bilgi Okuryazarlığı, OB2. Dijital Okuryazarlık, OB4. Görsel Okuryazarlık, OB6. Vatandaşlık Okuryazarlığı, OB9. Sanat Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="n"/>
-      <c r="G82" s="2" t="n"/>
-      <c r="H82" s="2" t="n"/>
-    </row>
-    <row r="83" ht="24.2" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="24.2" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>33-34. haftalar, 35. hafta</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n"/>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>OB5. Kültür Okuryazarlığı</t>
         </is>
       </c>
-      <c r="D83" s="2" t="n"/>
-      <c r="E83" s="2" t="n"/>
-      <c r="F83" s="2" t="n"/>
-      <c r="G83" s="2" t="n"/>
-      <c r="H83" s="2" t="n"/>
-    </row>
-    <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+    </row>
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>FARKLILAŞTIRMA</t>
         </is>
       </c>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="12" t="n"/>
-      <c r="D85" s="12" t="n"/>
-      <c r="E85" s="12" t="n"/>
-      <c r="F85" s="12" t="n"/>
-      <c r="G85" s="12" t="n"/>
-      <c r="H85" s="12" t="n"/>
-    </row>
-    <row r="86" ht="45.4" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="45.4" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Türkiye Yüzyılı Maarif Modeli Ortak Metni'nde “Farklılaştırılmış öğrenme yaşantılarında öğrencilerin ilgi alanları ile öğrenme profilleri önemlidir ve öğrencilere çeşitli öğrenme yaşantıları sunulur. Farklılaştırma kapsamında yapılacak zenginleştirme ve destekleme uygulamalarında öğrencilerin bireysel farklılıkları (öğrenme hızları, öğrenme stilleri, yetenekleri vb.), ilgi ve ihtiyaçları dikkate alınarak gereken planlamalar yapılır.” ifadesi yer almaktadır. Öğretmenler sınıftaki öğrencilerini gözlemleyerek gerek gördükleri konularda farklılaştırma uygulamalarını ders sürecine dâhil etmelidirler.</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n"/>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2" t="n"/>
-    </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>OKUL TEMELLİ PLANLAMA — ÇERÇEVE PLAN AÇIKLAMASI</t>
         </is>
       </c>
-      <c r="B88" s="12" t="n"/>
-      <c r="C88" s="12" t="n"/>
-      <c r="D88" s="12" t="n"/>
-      <c r="E88" s="12" t="n"/>
-      <c r="F88" s="12" t="n"/>
-      <c r="G88" s="12" t="n"/>
-      <c r="H88" s="12" t="n"/>
-    </row>
-    <row r="89" ht="66.59999999999999" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="12" t="n"/>
+      <c r="H40" s="12" t="n"/>
+    </row>
+    <row r="41" ht="66.59999999999999" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Okul temelli planlama; zümre öğretmenler kurulu tarafından ders kapsamında gerçekleştirilmesi kararlaştırılan araştırma ve gözlem, sosyal etkinlikler, proje çalışmaları, yerel çalışmalar, okuma çalışmaları vb. çalışmaları kapsamaktadır. Çalışmalar için ayrılan süre eğitim-öğretim yılı içinde planlanır ve yıllık planlarda ifade edilir. Bu planlamalar kapsamında yürütülecek öğretim faaliyetleri; öğrenci katılımını desteklemeli, yaparak ve yaşayarak öğrenmeye olanak tanımalı, öğrencinin bütüncül gelişime hizmet etmelidir. *Bu çerçeve planda belirtilen okul temelli planlama haftaları örnek olarak sunulmuştur. Zümre öğretmenler kurulunda aldığınız karara göre okul ve ders koşullarınıza uygun (öğretim programında belirtilen okul temelli planlama ders saati 2 haftadan fazla sürebilir) düzenleyebilirsiniz.</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n"/>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="n"/>
-      <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="n"/>
-    </row>
-    <row r="91" ht="14" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>OKUL UYARLAMA NOTLARI</t>
         </is>
       </c>
-      <c r="B91" s="12" t="n"/>
-      <c r="C91" s="12" t="n"/>
-      <c r="D91" s="12" t="n"/>
-      <c r="E91" s="12" t="n"/>
-      <c r="F91" s="12" t="n"/>
-      <c r="G91" s="12" t="n"/>
-      <c r="H91" s="12" t="n"/>
-    </row>
-    <row r="92" ht="24.2" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="n"/>
+    </row>
+    <row r="44" ht="24.2" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>GENEL ŞABLON: Bu plan, okulapp.org belge arşivinde yayımlanan genel sürümdür (CC BY 4.0). Köşeli parantezli KIRMIZI alanlar (okul adı, ad-soyad, tarih) okulun bilgileriyle doldurulur; doldurduktan sonra parantez kaldırılır ve yazı rengi siyaha çevrilir.</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n"/>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="n"/>
-    </row>
-    <row r="93" ht="34.8" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="34.8" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>KAYNAK: Bu plan, Millî Eğitim Bakanlığının tymm.meb.gov.tr/taslak-cerceve-planlari adresinde yayımladığı 2026-2027 eğitim öğretim yılı Anadolu lisesi coğrafya dersi taslak çerçeve yıllık planının "10.SINIF" sayfasından, içeriği değiştirilmeden A4 yatay sayfaya yeniden yerleştirilerek okula uyarlanmıştır (erişim 29.08.2026). Ünite bazlı öğrenme kanıtları ile programlar arası bileşenler, okunabilirlik için haftalık çizelgenin altındaki bölümlere taşınmıştır.</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n"/>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="2" t="n"/>
-      <c r="F93" s="2" t="n"/>
-      <c r="G93" s="2" t="n"/>
-      <c r="H93" s="2" t="n"/>
-    </row>
-    <row r="94" ht="45.4" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+    </row>
+    <row r="46" ht="45.4" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>ÇALIŞMA TAKVİMİ UYARLAMASI (il millî eğitim müdürlüğü 2026-2027 çalışma takvimi — tarihler Bakanlık takvimiyle ortaktır, ilinizin takvimini kontrol ediniz): Kurban Bayramı tatili 15-19 Mayıs 2027 olup planın 32. haftasına denk gelir; o hafta yalnız perşembe ve cuma günleri ders yapılır ve 19 Mayıs Atatürk'ü Anma, Gençlik ve Spor Bayramı bayram tatili içinde kalır. 28 Ekim 2026 çarşamba yarım gündür; 1 Ocak 2027 cuma ile 23 Nisan 2027 cuma resmî tatildir. Bu günlere gelen ders saatlerinde konu akışı zümre kararıyla yoğunlaştırılarak telafi edilir.</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n"/>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="n"/>
-      <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2" t="n"/>
-    </row>
-    <row r="95" ht="34.8" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+    </row>
+    <row r="47" ht="34.8" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>OKUL TEMELLİ PLANLAMA: Çizelgedeki kırmızı ekler zümre karar taslağıdır; sene başı zümre toplantısında kesinleştirilir, kesinleşen kullanım bu satırlara işlenerek kırmızı ibare siyaha çevrilir. Çerçeve plandaki 18. ve 36. hafta yerleşimi örnektir; zümre kararıyla değiştirilebilir. Öğrenme kanıtları zümre dosyasında toplanır; okul dışına çıkılan çalışmalarda zaman-yer-refakat onayı ile veli izni okulun sosyal etkinlik belgeleri üzerinden alınır.</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n"/>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="2" t="n"/>
-      <c r="G95" s="2" t="n"/>
-      <c r="H95" s="2" t="n"/>
-    </row>
-    <row r="96" ht="13.6" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="13.6" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>ÖLÇME VE DEĞERLENDİRME: Yazılı sınav tarihleri bu planda gösterilmez; okul sınav takvimi ve zümrenin ortak sınav planlamasına göre yürütülür.</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n"/>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="2" t="n"/>
-      <c r="H96" s="2" t="n"/>
-    </row>
-    <row r="97" ht="13.6" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+    </row>
+    <row r="49" ht="13.6" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>ATATÜRKÇÜLÜK KONULARI: 2488 sayılı Tebliğler Dergisi'ndeki Atatürkçülük konuları, zümre kararı doğrultusunda ilgili ünitelere dağıtılarak işlenir.</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n"/>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="2" t="n"/>
-      <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2" t="n"/>
-    </row>
-    <row r="99" ht="24.2" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+    </row>
+    <row r="51" ht="24.2" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bu yıllık plan, Eğitim ve Öğretim Çalışmalarının Planlı Yürütülmesine İlişkin Yönergenin 9 uncu ve 10 uncu maddeleri uyarınca coğrafya zümre öğretmenlerince ortak hazırlanarak okul müdürlüğüne sunulmuştur. Tarih: </t>
@@ -2465,304 +2585,247 @@
           </r>
         </is>
       </c>
-      <c r="B99" s="2" t="n"/>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n"/>
-      <c r="E99" s="2" t="n"/>
-      <c r="F99" s="2" t="n"/>
-      <c r="G99" s="2" t="n"/>
-      <c r="H99" s="2" t="n"/>
-    </row>
-    <row r="101" ht="13" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Adı Soyadı</t>
         </is>
       </c>
-      <c r="B101" s="12" t="n"/>
-      <c r="C101" s="12" t="n"/>
-      <c r="D101" s="12" t="n"/>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="B53" s="12" t="n"/>
+      <c r="C53" s="12" t="n"/>
+      <c r="D53" s="12" t="n"/>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Görevi</t>
         </is>
       </c>
-      <c r="F101" s="12" t="n"/>
-      <c r="G101" s="3" t="inlineStr">
+      <c r="F53" s="12" t="n"/>
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>İmza</t>
         </is>
       </c>
-      <c r="H101" s="12" t="n"/>
-    </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="13" t="inlineStr">
+      <c r="H53" s="12" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni (Zümre Başkanı)</t>
         </is>
       </c>
-      <c r="F102" s="2" t="n"/>
-      <c r="G102" s="5" t="n"/>
-      <c r="H102" s="2" t="n"/>
-    </row>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="13" t="inlineStr">
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n"/>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="5" t="n"/>
-      <c r="H103" s="2" t="n"/>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="13" t="inlineStr">
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n"/>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="2" t="n"/>
-    </row>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="13" t="inlineStr">
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="2" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B105" s="2" t="n"/>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F105" s="2" t="n"/>
-      <c r="G105" s="5" t="n"/>
-      <c r="H105" s="2" t="n"/>
-    </row>
-    <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="13" t="inlineStr">
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="2" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
-      <c r="B106" s="2" t="n"/>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Coğrafya Öğretmeni</t>
         </is>
       </c>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="5" t="n"/>
-      <c r="H106" s="2" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="14" t="inlineStr">
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>UYGUNDUR</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="15" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
         <is>
           <t>[../09/2026]</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="16" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="17" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>Okul Müdürü</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="148">
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="A77:H77"/>
-    <mergeCell ref="C55:H55"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="C75:H75"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A110:H110"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="C52:H52"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C72:H72"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="A86:H86"/>
-    <mergeCell ref="A95:H95"/>
-    <mergeCell ref="C78:H78"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A96:H96"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="C79:H79"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="C73:H73"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="C63:H63"/>
+  <mergeCells count="91">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E55:F55"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A60:H60"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A108:H108"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="C69:H69"/>
-    <mergeCell ref="C83:H83"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="C64:H64"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="C54:H54"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="C56:H56"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="D31:D38"/>
-    <mergeCell ref="C71:H71"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C82:H82"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C57:H57"/>
-    <mergeCell ref="C66:H66"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C53:H53"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="A109:H109"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="A104:D104"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A111:H111"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="C65:H65"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="A106:D106"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="C80:H80"/>
-    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C31:H31"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="A94:H94"/>
-    <mergeCell ref="C70:H70"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="D14:D18"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A89:H89"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C74:H74"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A93:H93"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.39" right="0.39" top="0.55" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-002_Cografya_10_Sinif_Yillik_Plani_v1.0.xlsx
+++ b/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-002_Cografya_10_Sinif_Yillik_Plani_v1.0.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="1" max="1"/>
@@ -1712,66 +1712,6 @@
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
       <c r="H43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n"/>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="n"/>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="n"/>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="n"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="58">

--- a/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-002_Cografya_10_Sinif_Yillik_Plani_v1.0.xlsx
+++ b/public/evrak/cografya-yillik-planlari/GNL-CYP-CP-002_Cografya_10_Sinif_Yillik_Plani_v1.0.xlsx
@@ -1793,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="1" max="1"/>
@@ -2442,7 +2442,7 @@
     <row r="45" ht="34.8" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>KAYNAK: Bu plan, Millî Eğitim Bakanlığının tymm.meb.gov.tr/taslak-cerceve-planlari adresinde yayımladığı 2026-2027 eğitim öğretim yılı Anadolu lisesi coğrafya dersi taslak çerçeve yıllık planının "10.SINIF" sayfasından, içeriği değiştirilmeden A4 yatay sayfaya yeniden yerleştirilerek okula uyarlanmıştır (erişim 29.08.2026). Ünite bazlı öğrenme kanıtları ile programlar arası bileşenler, okunabilirlik için haftalık çizelgenin altındaki bölümlere taşınmıştır.</t>
+          <t>ÖĞRETİM PROGRAMI: Bu plan, Coğrafya Dersi Öğretim Programına (Türkiye Yüzyılı Maarif Modeli) göre hazırlanmıştır. Program, Talim ve Terbiye Kurulunun 23.05.2024 tarihli ve 20 sayılı kararıyla kabul edilmiş; Kurulun 13.05.2026 tarihli ve 53 sayılı kararıyla değişiklik yapılarak 2026-2027 eğitim ve öğretim yılında 9, 10 ve 11. sınıf seviyelerinde uygulanmak üzere yürürlüğe konulmuştur. Esas alınacak metin programın 2026 nüshasıdır (mufredat.meb.gov.tr).</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -2453,10 +2453,10 @@
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
     </row>
-    <row r="46" ht="45.4" customHeight="1">
+    <row r="46" ht="34.8" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>ÇALIŞMA TAKVİMİ UYARLAMASI (il millî eğitim müdürlüğü 2026-2027 çalışma takvimi — tarihler Bakanlık takvimiyle ortaktır, ilinizin takvimini kontrol ediniz): Kurban Bayramı tatili 15-19 Mayıs 2027 olup planın 32. haftasına denk gelir; o hafta yalnız perşembe ve cuma günleri ders yapılır ve 19 Mayıs Atatürk'ü Anma, Gençlik ve Spor Bayramı bayram tatili içinde kalır. 28 Ekim 2026 çarşamba yarım gündür; 1 Ocak 2027 cuma ile 23 Nisan 2027 cuma resmî tatildir. Bu günlere gelen ders saatlerinde konu akışı zümre kararıyla yoğunlaştırılarak telafi edilir.</t>
+          <t>KAYNAK: Bu plan, Millî Eğitim Bakanlığının tymm.meb.gov.tr/taslak-cerceve-planlari adresinde yayımladığı 2026-2027 eğitim öğretim yılı Anadolu lisesi coğrafya dersi taslak çerçeve yıllık planının "10.SINIF" sayfasından, içeriği değiştirilmeden A4 yatay sayfaya yeniden yerleştirilerek okula uyarlanmıştır (erişim 29.08.2026). Ünite bazlı öğrenme kanıtları ile programlar arası bileşenler, okunabilirlik için haftalık çizelgenin altındaki bölümlere taşınmıştır.</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -2467,10 +2467,10 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
-    <row r="47" ht="34.8" customHeight="1">
+    <row r="47" ht="45.4" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>OKUL TEMELLİ PLANLAMA: Çizelgedeki kırmızı ekler zümre karar taslağıdır; sene başı zümre toplantısında kesinleştirilir, kesinleşen kullanım bu satırlara işlenerek kırmızı ibare siyaha çevrilir. Çerçeve plandaki 18. ve 36. hafta yerleşimi örnektir; zümre kararıyla değiştirilebilir. Öğrenme kanıtları zümre dosyasında toplanır; okul dışına çıkılan çalışmalarda zaman-yer-refakat onayı ile veli izni okulun sosyal etkinlik belgeleri üzerinden alınır.</t>
+          <t>ÇALIŞMA TAKVİMİ UYARLAMASI (il millî eğitim müdürlüğü 2026-2027 çalışma takvimi — tarihler Bakanlık takvimiyle ortaktır, ilinizin takvimini kontrol ediniz): Kurban Bayramı tatili 15-19 Mayıs 2027 olup planın 32. haftasına denk gelir; o hafta yalnız perşembe ve cuma günleri ders yapılır ve 19 Mayıs Atatürk'ü Anma, Gençlik ve Spor Bayramı bayram tatili içinde kalır. 28 Ekim 2026 çarşamba yarım gündür; 1 Ocak 2027 cuma ile 23 Nisan 2027 cuma resmî tatildir. Bu günlere gelen ders saatlerinde konu akışı zümre kararıyla yoğunlaştırılarak telafi edilir.</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -2481,10 +2481,10 @@
       <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
     </row>
-    <row r="48" ht="13.6" customHeight="1">
+    <row r="48" ht="34.8" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>ÖLÇME VE DEĞERLENDİRME: Yazılı sınav tarihleri bu planda gösterilmez; okul sınav takvimi ve zümrenin ortak sınav planlamasına göre yürütülür.</t>
+          <t>OKUL TEMELLİ PLANLAMA: Çizelgedeki kırmızı ekler zümre karar taslağıdır; sene başı zümre toplantısında kesinleştirilir, kesinleşen kullanım bu satırlara işlenerek kırmızı ibare siyaha çevrilir. Çerçeve plandaki 18. ve 36. hafta yerleşimi örnektir; zümre kararıyla değiştirilebilir. Öğrenme kanıtları zümre dosyasında toplanır; okul dışına çıkılan çalışmalarda zaman-yer-refakat onayı ile veli izni okulun sosyal etkinlik belgeleri üzerinden alınır.</t>
         </is>
       </c>
       <c r="B48" s="2" t="n"/>
@@ -2498,7 +2498,7 @@
     <row r="49" ht="13.6" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>ATATÜRKÇÜLÜK KONULARI: 2488 sayılı Tebliğler Dergisi'ndeki Atatürkçülük konuları, zümre kararı doğrultusunda ilgili ünitelere dağıtılarak işlenir.</t>
+          <t>ÖLÇME VE DEĞERLENDİRME: Yazılı sınav tarihleri bu planda gösterilmez; okul sınav takvimi ve zümrenin ortak sınav planlamasına göre yürütülür.</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -2509,8 +2509,22 @@
       <c r="G49" s="2" t="n"/>
       <c r="H49" s="2" t="n"/>
     </row>
-    <row r="51" ht="24.2" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="50" ht="13.6" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>ATATÜRKÇÜLÜK KONULARI: 2488 sayılı Tebliğler Dergisi'ndeki Atatürkçülük konuları, zümre kararı doğrultusunda ilgili ünitelere dağıtılarak işlenir.</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+    </row>
+    <row r="52" ht="24.2" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Bu yıllık plan, Eğitim ve Öğretim Çalışmalarının Planlı Yürütülmesine İlişkin Yönergenin 9 uncu ve 10 uncu maddeleri uyarınca coğrafya zümre öğretmenlerince ortak hazırlanarak okul müdürlüğüne sunulmuştur. Tarih: </t>
@@ -2525,53 +2539,35 @@
           </r>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Adı Soyadı</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n"/>
-      <c r="C53" s="12" t="n"/>
-      <c r="D53" s="12" t="n"/>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="12" t="n"/>
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Görevi</t>
         </is>
       </c>
-      <c r="F53" s="12" t="n"/>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="F54" s="12" t="n"/>
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>İmza</t>
         </is>
       </c>
-      <c r="H53" s="12" t="n"/>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>[Adı SOYADI]</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Coğrafya Öğretmeni (Zümre Başkanı)</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="2" t="n"/>
+      <c r="H54" s="12" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="13" t="inlineStr">
@@ -2584,7 +2580,7 @@
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Coğrafya Öğretmeni</t>
+          <t>Coğrafya Öğretmeni (Zümre Başkanı)</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
@@ -2645,36 +2641,54 @@
       <c r="G58" s="5" t="n"/>
       <c r="H58" s="2" t="n"/>
     </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>[Adı SOYADI]</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Coğrafya Öğretmeni</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>UYGUNDUR</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="15" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>[../09/2026]</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>[Adı SOYADI]</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="17" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Okul Müdürü</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="92">
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C9:H9"/>
@@ -2683,6 +2697,7 @@
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="G57:H57"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="C13:H13"/>
@@ -2693,22 +2708,20 @@
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="C24:H24"/>
-    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="E53:F53"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A40:H40"/>
+    <mergeCell ref="G59:H59"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A53:D53"/>
     <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="A8:B8"/>
@@ -2722,11 +2735,13 @@
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A64:H64"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="C17:H17"/>
+    <mergeCell ref="E59:F59"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A32:B32"/>
@@ -2752,7 +2767,6 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="C23:H23"/>
-    <mergeCell ref="G53:H53"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A46:H46"/>
@@ -2762,6 +2776,7 @@
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C35:H35"/>
